--- a/ZOI-SL-IL-7201/D5. File Aksesoris ZOI-SL-IL-7201.xlsx
+++ b/ZOI-SL-IL-7201/D5. File Aksesoris ZOI-SL-IL-7201.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\R&amp;D PT. Cahaya Hasil Cemerlang Multi Manufaktur\PERSIAPAN IZIN EDAR\SURGICAL LIGHT\8. ZOI-SL-IL-5201 ZOI Ilios 5000 Series Surgical Light - Double Dome  dengan Hanging Monitor dan Built-in Camera\DOKUMEN TEKNIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb713085e485f505/Desktop/IZIN EDAR SURGICAL LIGHT TERBARU/ZOI-SL-IL-5101/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE53741C-5239-4A06-8961-E56C378EE61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{F77A6375-5F28-4EF9-AFF9-24D8CCBC7380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3638F98D-3D8E-41CE-88A7-5ED117EE9660}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aksesoris" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Data Aksesoris format File Excel</t>
   </si>
@@ -67,39 +67,18 @@
     <t>Sebagai form kartu garansi</t>
   </si>
   <si>
-    <t>UPS (Uninterruptible Power Supply)</t>
-  </si>
-  <si>
-    <t>Sebagai catu daya cadangan ketika tidak mendapatkan suplai listrik</t>
-  </si>
-  <si>
     <t>Hand Controller</t>
   </si>
   <si>
     <t xml:space="preserve">Sebagai kontroler jarak jauh berupa remote untuk mengontrol kamera dan lampu </t>
   </si>
   <si>
-    <t>Monitor + Hanging Suspension</t>
-  </si>
-  <si>
-    <t>Sebagai monitor yang menampilkan hasil perekaman video oleh kamera</t>
-  </si>
-  <si>
-    <t>Built-in Camera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebagai alat perekam video </t>
-  </si>
-  <si>
     <t>DVR</t>
   </si>
   <si>
     <t>Sebagai alat perekam gambar / video kedalam penyimpanan / Harddisk</t>
   </si>
   <si>
-    <t>Converter</t>
-  </si>
-  <si>
     <t>Sebagai alat konversi koneksi media DVI to HDMI atau sebaliknya</t>
   </si>
   <si>
@@ -107,6 +86,57 @@
   </si>
   <si>
     <t>Sebagai kabel spliter untuk memperbanyak kabel output video yang dinginkan</t>
+  </si>
+  <si>
+    <t>Converter Module</t>
+  </si>
+  <si>
+    <t>Wall Control panel</t>
+  </si>
+  <si>
+    <t>Wall 55" 4K UHD Monitor</t>
+  </si>
+  <si>
+    <t>Hanging Suspension</t>
+  </si>
+  <si>
+    <t>Sebagai Hanging Tempat Monitor</t>
+  </si>
+  <si>
+    <t>Built-in HD Camera</t>
+  </si>
+  <si>
+    <t>Sebagai alat perekam video  kualitas HD</t>
+  </si>
+  <si>
+    <t>Sebagai monitor kualitas HD yang menampilkan hasil perekaman video oleh kamera</t>
+  </si>
+  <si>
+    <t>Built-in 4K UHD Camera</t>
+  </si>
+  <si>
+    <t>Sebagai pengontrol lampu yang menempel pada tembok</t>
+  </si>
+  <si>
+    <t>Sebagai monitor kualitas 4K UHD untuk menampilkan hasil perekaman video oleh kamera</t>
+  </si>
+  <si>
+    <t>Sebagai monitor kualitas 4K UHD yang menampilkan hasil perekaman video oleh kamera</t>
+  </si>
+  <si>
+    <t>Sebagai alat perekam video  kualitas 4K UHD</t>
+  </si>
+  <si>
+    <t>Kabel HDMI</t>
+  </si>
+  <si>
+    <t>Sebagai kabel penyalur multimedia dari DVR / Splitter menuju ke Monitor</t>
+  </si>
+  <si>
+    <t>HD Monitor</t>
+  </si>
+  <si>
+    <t>4K UHD Monitor</t>
   </si>
 </sst>
 </file>
@@ -242,7 +272,7 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{B7B0C4B3-91D2-474B-BD19-CC02C8835ECD}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{BCF22113-67E3-4CFF-8045-2F5A61E1B302}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -597,7 +627,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>2</v>
       </c>
@@ -614,23 +644,23 @@
         <v>3</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>4</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -638,23 +668,23 @@
         <v>5</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="4" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -662,100 +692,120 @@
         <v>7</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>9</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>10</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>12</v>
       </c>
-      <c r="B18" s="9"/>
+      <c r="B18" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>13</v>
       </c>
-      <c r="B19" s="9"/>
+      <c r="B19" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>14</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>15</v>
       </c>
-      <c r="B21" s="9"/>
+      <c r="B21" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>16</v>
       </c>
-      <c r="B22" s="9"/>
+      <c r="B22" s="9" t="s">
+        <v>13</v>
+      </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
